--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_advanced_features.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_advanced_features.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824B08BC-82CE-42B4-80F3-1F3B80C4BED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A4F33F-9615-4554-A5B0-AFD23771AED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
   <sheets>
     <sheet name="veda input" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="dcost_data" sheetId="6" r:id="rId4"/>
     <sheet name="readme_dcost" sheetId="5" r:id="rId5"/>
     <sheet name="uc_tech_map" sheetId="4" r:id="rId6"/>
+    <sheet name="DEF topology" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_CH">110000</definedName>
@@ -67,8 +68,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={F4E4F727-2A91-4760-B84E-3C8E8E996337}</author>
+  </authors>
+  <commentList>
+    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{F4E4F727-2A91-4760-B84E-3C8E8E996337}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    CAP (nonRE) &gt; COMPRD (DEF_C) </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="278">
   <si>
     <t>ACT_MINLD</t>
   </si>
@@ -2599,21 +2618,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Sources:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> All cost estimates are derived from industry reports and case studies. For example, Raimi (2017) provides average and range for U.S. plant decommissioning costs by fuel, which we have updated to 2023 USD. Additional data from World Bank/ESMAP, Gold Standard, NewClimate Institute, and World Nuclear Association/IAEA inform the figures. Where specific technologies have not yet been decommissioned (e.g. CCS-equipped plants, SMRs), we have indicated that no direct sources exist and provided reasoned estimates (with assumptions noted). All ranges reflect low/high scenarios; higher-end costs usually assume more extensive environmental remediation per regional regulatory requirements.</t>
-    </r>
-  </si>
-  <si>
     <t>decomissioning_cost</t>
   </si>
   <si>
@@ -2765,13 +2769,103 @@
   </si>
   <si>
     <t>Nuclear P</t>
+  </si>
+  <si>
+    <t>~TFM_TOPINS</t>
+  </si>
+  <si>
+    <t>process</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>io</t>
+  </si>
+  <si>
+    <t>*stg8hb*</t>
+  </si>
+  <si>
+    <t>ELC4H,ELC8H,ELC</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>*stg4hb*</t>
+  </si>
+  <si>
+    <t>ELC4H,ELC</t>
+  </si>
+  <si>
+    <t>distr*</t>
+  </si>
+  <si>
+    <t>ELC4H,ELC8H</t>
+  </si>
+  <si>
+    <t>OUT</t>
+  </si>
+  <si>
+    <t>~UC_Sets: R_E: AllRegions</t>
+  </si>
+  <si>
+    <t>~UC_T: LO</t>
+  </si>
+  <si>
+    <t>UC_N</t>
+  </si>
+  <si>
+    <t>PSET_PN</t>
+  </si>
+  <si>
+    <t>Pset_CI</t>
+  </si>
+  <si>
+    <t>PSET_CO</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>UC_CAP</t>
+  </si>
+  <si>
+    <t>UC_COMPRD</t>
+  </si>
+  <si>
+    <t>UC_RHSRT</t>
+  </si>
+  <si>
+    <t>UC_RHSRT~0</t>
+  </si>
+  <si>
+    <t>UC_Desc</t>
+  </si>
+  <si>
+    <t>UCE_Min-DispatchableCAP</t>
+  </si>
+  <si>
+    <t>ELE,CHP</t>
+  </si>
+  <si>
+    <t>*,-solar,-wind*,-ELC,-ELCSPV,-elc[_]???[_]*,-e[_]*</t>
+  </si>
+  <si>
+    <t>Min dispatchable capacity for VRE portfolio</t>
+  </si>
+  <si>
+    <t>DEF_C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2843,8 +2937,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2854,6 +2954,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2890,7 +2996,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
@@ -2930,6 +3036,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Good" xfId="3" builtinId="26"/>
@@ -2948,6 +3055,87 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>545307</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>176211</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2976562</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>4763</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BDC4EF9-5E8A-2F58-6455-1CFB661B4753}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="545307" y="40285986"/>
+          <a:ext cx="8170068" cy="1276352"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>Sources: All cost estimates are derived from industry reports and case studies. For example, Raimi (2017) provides average and range for U.S. plant decommissioning costs by fuel, which we have updated to 2023 USD. Additional data from World Bank/ESMAP, Gold Standard, NewClimate Institute, and World Nuclear Association/IAEA inform the figures. Where specific technologies have not yet been decommissioned (e.g. CCS-equipped plants, SMRs), we have indicated that no direct sources exist and provided reasoned estimates (with assumptions noted). All ranges reflect low/high scenarios; higher-end costs usually assume more extensive environmental remediation per regional regulatory requirements.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="黄 凱凱(Kaikai Huang)" id="{EA662EF9-C1C3-4C75-9049-4457D0909F07}" userId="S::J2412140@jera.co.jp::f9b6adb6-b751-4da6-9b6e-314b902b48bf" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3245,6 +3433,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="H20" dT="2026-04-17T06:07:36.14" personId="{EA662EF9-C1C3-4C75-9049-4457D0909F07}" id="{F4E4F727-2A91-4760-B84E-3C8E8E996337}">
+    <text xml:space="preserve">CAP (nonRE) &gt; COMPRD (DEF_C) </text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75F77616-F3F2-4CAD-9718-D78F2778A52A}">
   <dimension ref="B2:S17"/>
@@ -3273,7 +3469,7 @@
   <sheetData>
     <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="D2" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>90</v>
@@ -3311,7 +3507,7 @@
         <v>82</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M3" s="9"/>
       <c r="N3" s="3" t="s">
@@ -4073,7 +4269,7 @@
         <v>0.1</v>
       </c>
       <c r="H17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>83</v>
@@ -4162,39 +4358,39 @@
   <sheetData>
     <row r="2" spans="2:50" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="AD2" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="3" spans="2:50" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" t="s">
         <v>203</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>204</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>205</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>206</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>207</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>208</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>209</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>210</v>
-      </c>
-      <c r="J3" t="s">
-        <v>211</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -4242,7 +4438,7 @@
         <v>200</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AE3" s="3">
         <f t="shared" ref="AE3:AS4" si="0">K3</f>
@@ -4307,25 +4503,25 @@
     </row>
     <row r="4" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4" t="s">
         <v>213</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>214</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F4" t="s">
         <v>215</v>
-      </c>
-      <c r="E4" t="s">
-        <v>215</v>
-      </c>
-      <c r="F4" t="s">
-        <v>216</v>
       </c>
       <c r="G4" s="17">
         <v>39.18</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I4" s="17">
         <v>43.5</v>
@@ -4445,25 +4641,25 @@
     </row>
     <row r="5" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" t="s">
         <v>218</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F5" t="s">
         <v>215</v>
-      </c>
-      <c r="D5" t="s">
-        <v>219</v>
-      </c>
-      <c r="E5" t="s">
-        <v>215</v>
-      </c>
-      <c r="F5" t="s">
-        <v>216</v>
       </c>
       <c r="G5" s="17">
         <v>19.34</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I5" s="17">
         <v>28.67</v>
@@ -4583,30 +4779,30 @@
     </row>
     <row r="7" spans="2:50" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AD7" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="2:50" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C8" t="s">
         <v>203</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>204</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>205</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>206</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>207</v>
       </c>
-      <c r="G8" t="s">
-        <v>208</v>
-      </c>
       <c r="H8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -4669,7 +4865,7 @@
         <v>200</v>
       </c>
       <c r="AD8" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AE8" s="3">
         <f t="shared" ref="AE8:AT10" si="2">I8</f>
@@ -4754,19 +4950,19 @@
     </row>
     <row r="9" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" t="s">
+        <v>214</v>
+      </c>
+      <c r="F9" t="s">
         <v>220</v>
-      </c>
-      <c r="C9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E9" t="s">
-        <v>215</v>
-      </c>
-      <c r="F9" t="s">
-        <v>221</v>
       </c>
       <c r="G9" s="17">
         <v>30.18</v>
@@ -4921,19 +5117,19 @@
     </row>
     <row r="10" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G10" s="17">
         <v>19.73</v>
@@ -5088,47 +5284,47 @@
     </row>
     <row r="13" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B13" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B14" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
     </row>
     <row r="15" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B15" s="18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
     </row>
     <row r="16" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B16" s="18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B18" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="D18" s="18" t="s">
         <v>228</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B19" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>230</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>231</v>
       </c>
       <c r="D19" s="18">
         <v>253</v>
@@ -5136,36 +5332,36 @@
     </row>
     <row r="20" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D20" s="18">
         <v>203</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B21" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C21" s="18" t="s">
         <v>234</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>235</v>
       </c>
       <c r="D21" s="18">
         <v>82</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="K21" s="3">
         <v>2019</v>
@@ -5176,22 +5372,22 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B22" s="18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D22" s="18">
         <v>242</v>
       </c>
       <c r="H22" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I22" t="s">
+        <v>245</v>
+      </c>
+      <c r="J22" t="s">
         <v>246</v>
-      </c>
-      <c r="J22" t="s">
-        <v>247</v>
       </c>
       <c r="K22">
         <f>AD4</f>
@@ -5203,16 +5399,16 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B23" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D23" s="18">
         <v>226</v>
       </c>
       <c r="H23" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I23" t="s">
         <v>80</v>
@@ -5227,16 +5423,16 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B24" s="18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D24" s="18">
         <v>174</v>
       </c>
       <c r="H24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
@@ -5251,16 +5447,16 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B25" s="18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D25" s="18">
         <v>258</v>
       </c>
       <c r="H25" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I25" t="s">
         <v>15</v>
@@ -5275,10 +5471,10 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B26" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="C26" s="18" t="s">
         <v>244</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>245</v>
       </c>
       <c r="D26" s="18">
         <v>135</v>
@@ -5967,7 +6163,7 @@
         <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
@@ -6501,12 +6697,11 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A25" s="15" t="s">
-        <v>197</v>
-      </c>
+      <c r="A25" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6585,4 +6780,148 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7792CB6B-18A0-47FE-98AC-84F99BF1E696}">
+  <dimension ref="B3:M23"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B3" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" t="s">
+        <v>256</v>
+      </c>
+      <c r="D6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>257</v>
+      </c>
+      <c r="C7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="H20" s="19" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>262</v>
+      </c>
+      <c r="C21" t="s">
+        <v>236</v>
+      </c>
+      <c r="D21" t="s">
+        <v>263</v>
+      </c>
+      <c r="E21" t="s">
+        <v>264</v>
+      </c>
+      <c r="F21" t="s">
+        <v>265</v>
+      </c>
+      <c r="G21" t="s">
+        <v>266</v>
+      </c>
+      <c r="H21" t="s">
+        <v>267</v>
+      </c>
+      <c r="I21" t="s">
+        <v>268</v>
+      </c>
+      <c r="J21" t="s">
+        <v>269</v>
+      </c>
+      <c r="K21" t="s">
+        <v>270</v>
+      </c>
+      <c r="L21" t="s">
+        <v>271</v>
+      </c>
+      <c r="M21" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>273</v>
+      </c>
+      <c r="C22" t="s">
+        <v>274</v>
+      </c>
+      <c r="E22" t="s">
+        <v>275</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>5</v>
+      </c>
+      <c r="M22" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="G23" t="s">
+        <v>277</v>
+      </c>
+      <c r="J23">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_advanced_features.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_advanced_features.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A4F33F-9615-4554-A5B0-AFD23771AED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B6907D-6C39-452D-B64B-38F32025EB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
   <sheets>
     <sheet name="veda input" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="280">
   <si>
     <t>ACT_MINLD</t>
   </si>
@@ -2859,13 +2859,19 @@
   </si>
   <si>
     <t>DEF_C</t>
+  </si>
+  <si>
+    <t>Gas Turbine*</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2937,12 +2943,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2996,7 +2996,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
@@ -3037,6 +3037,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Good" xfId="3" builtinId="26"/>
@@ -3443,7 +3447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75F77616-F3F2-4CAD-9718-D78F2778A52A}">
-  <dimension ref="B2:S17"/>
+  <dimension ref="B2:S18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.73046875" bestFit="1" customWidth="1"/>
@@ -4301,6 +4305,52 @@
         <v>-aggregated*</v>
       </c>
     </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B18" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="22">
+        <v>0</v>
+      </c>
+      <c r="E18" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="F18" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="G18" s="22">
+        <v>0.01</v>
+      </c>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="L18" s="23">
+        <v>30</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="O18" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="R18" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="S18" s="22" t="s">
+        <v>278</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:P17">
     <sortCondition ref="A4:A17"/>
@@ -4311,7 +4361,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA60F42B-F2D1-44E2-B5F0-15531EB389CB}">
-  <dimension ref="B2:AX26"/>
+  <dimension ref="B2:BH26"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
@@ -4335,36 +4385,42 @@
     <col min="24" max="24" width="5" bestFit="1" customWidth="1"/>
     <col min="25" max="26" width="6" bestFit="1" customWidth="1"/>
     <col min="27" max="28" width="4" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.53125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="3" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="6" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="3" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="5" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="5" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="6" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="4" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="5" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="6" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="4" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="5" bestFit="1" customWidth="1"/>
-    <col min="49" max="50" width="4" bestFit="1" customWidth="1"/>
+    <col min="29" max="34" width="4" style="20" customWidth="1"/>
+    <col min="36" max="36" width="14.53125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="1.73046875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="59" max="60" width="4.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:50" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:60" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="3" spans="2:50" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:60" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B3" t="s">
         <v>202</v>
       </c>
@@ -4405,103 +4461,186 @@
         <v>41</v>
       </c>
       <c r="O3">
+        <f>N3+18</f>
+        <v>59</v>
+      </c>
+      <c r="P3">
+        <f>O3+1</f>
+        <v>60</v>
+      </c>
+      <c r="Q3">
+        <f>P3+1</f>
+        <v>61</v>
+      </c>
+      <c r="R3" s="20">
+        <f>Q3+18</f>
         <v>79</v>
       </c>
-      <c r="P3">
+      <c r="S3" s="20">
+        <f>R3+1</f>
         <v>80</v>
       </c>
-      <c r="Q3">
+      <c r="T3" s="20">
+        <f>S3+1</f>
         <v>81</v>
       </c>
-      <c r="R3">
+      <c r="U3" s="20">
+        <f>T3+18</f>
+        <v>99</v>
+      </c>
+      <c r="V3" s="20">
+        <f>U3+1</f>
+        <v>100</v>
+      </c>
+      <c r="W3" s="20">
+        <f>V3+1</f>
+        <v>101</v>
+      </c>
+      <c r="X3" s="20">
+        <f>W3+18</f>
         <v>119</v>
       </c>
-      <c r="S3">
+      <c r="Y3" s="20">
+        <f>X3+1</f>
         <v>120</v>
       </c>
-      <c r="T3">
+      <c r="Z3" s="20">
+        <f>Y3+1</f>
         <v>121</v>
       </c>
-      <c r="U3">
+      <c r="AA3" s="20">
+        <f>Z3+18</f>
+        <v>139</v>
+      </c>
+      <c r="AB3" s="20">
+        <f>AA3+1</f>
+        <v>140</v>
+      </c>
+      <c r="AC3" s="20">
+        <f>AB3+1</f>
+        <v>141</v>
+      </c>
+      <c r="AD3" s="20">
+        <f>AC3+18</f>
         <v>159</v>
       </c>
-      <c r="V3">
+      <c r="AE3" s="20">
+        <f>AD3+1</f>
         <v>160</v>
       </c>
-      <c r="W3">
+      <c r="AF3" s="20">
+        <f>AE3+1</f>
         <v>161</v>
       </c>
-      <c r="X3">
-        <v>199</v>
-      </c>
-      <c r="Y3">
-        <v>200</v>
-      </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AG3" s="20">
+        <f>AF3+18</f>
+        <v>179</v>
+      </c>
+      <c r="AH3" s="20">
+        <f>AG3+1</f>
+        <v>180</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="AE3" s="3">
-        <f t="shared" ref="AE3:AS4" si="0">K3</f>
-        <v>1</v>
-      </c>
-      <c r="AF3" s="3">
+      <c r="AK3" s="3">
+        <f t="shared" ref="AK3:AY4" si="0">K3</f>
+        <v>1</v>
+      </c>
+      <c r="AL3" s="3">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="AG3" s="3">
+      <c r="AM3" s="3">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="AH3" s="3">
+      <c r="AN3" s="3">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="AI3" s="3">
+      <c r="AO3" s="3">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="AP3" s="3">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="AQ3" s="3">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="AR3" s="3">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
-      <c r="AJ3" s="3">
+      <c r="AS3" s="3">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="AK3" s="3">
+      <c r="AT3" s="3">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="AL3" s="3">
+      <c r="AU3" s="3">
+        <f t="shared" si="0"/>
+        <v>99</v>
+      </c>
+      <c r="AV3" s="3">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="AW3" s="3">
+        <f t="shared" si="0"/>
+        <v>101</v>
+      </c>
+      <c r="AX3" s="3">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
-      <c r="AM3" s="3">
+      <c r="AY3" s="3">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="AN3" s="3">
-        <f t="shared" si="0"/>
+      <c r="AZ3" s="21">
+        <f t="shared" ref="AZ3:AZ5" si="1">Z3</f>
         <v>121</v>
       </c>
-      <c r="AO3" s="3">
-        <f t="shared" si="0"/>
+      <c r="BA3" s="21">
+        <f t="shared" ref="BA3:BA5" si="2">AA3</f>
+        <v>139</v>
+      </c>
+      <c r="BB3" s="21">
+        <f t="shared" ref="BB3:BB5" si="3">AB3</f>
+        <v>140</v>
+      </c>
+      <c r="BC3" s="21">
+        <f t="shared" ref="BC3:BC5" si="4">AC3</f>
+        <v>141</v>
+      </c>
+      <c r="BD3" s="21">
+        <f t="shared" ref="BD3:BE5" si="5">AD3</f>
         <v>159</v>
       </c>
-      <c r="AP3" s="3">
-        <f t="shared" si="0"/>
+      <c r="BE3" s="21">
+        <f t="shared" si="5"/>
         <v>160</v>
       </c>
-      <c r="AQ3" s="3">
-        <f t="shared" si="0"/>
+      <c r="BF3" s="21">
+        <f t="shared" ref="BF3:BF5" si="6">AF3</f>
         <v>161</v>
       </c>
-      <c r="AR3" s="3">
-        <f t="shared" si="0"/>
-        <v>199</v>
-      </c>
-      <c r="AS3" s="3">
-        <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="4" spans="2:50" x14ac:dyDescent="0.45">
+      <c r="BG3" s="21">
+        <f t="shared" ref="BG3:BG5" si="7">AG3</f>
+        <v>179</v>
+      </c>
+      <c r="BH3" s="21">
+        <f t="shared" ref="BH3:BH5" si="8">AH3</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="2:60" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>212</v>
       </c>
@@ -4574,33 +4713,45 @@
       <c r="Y4">
         <v>6.18</v>
       </c>
-      <c r="AD4">
-        <f t="shared" ref="AD4:AS5" si="1">J4</f>
+      <c r="Z4">
+        <f>W4</f>
+        <v>1</v>
+      </c>
+      <c r="AA4" s="20">
+        <f t="shared" ref="AA4:AE5" si="9">X4</f>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="AB4" s="20">
+        <f t="shared" si="9"/>
+        <v>6.18</v>
+      </c>
+      <c r="AC4" s="20">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AD4" s="20">
+        <f t="shared" si="9"/>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="AE4" s="20">
+        <f t="shared" si="9"/>
+        <v>6.18</v>
+      </c>
+      <c r="AF4" s="20">
+        <f t="shared" ref="AF4:AF5" si="10">AC4</f>
+        <v>1</v>
+      </c>
+      <c r="AG4" s="20">
+        <f t="shared" ref="AG4:AG5" si="11">AD4</f>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="AH4" s="20">
+        <f t="shared" ref="AH4:AH5" si="12">AE4</f>
+        <v>6.18</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" ref="AJ4:AY5" si="13">J4</f>
         <v>81</v>
-      </c>
-      <c r="AE4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AF4">
-        <f t="shared" si="0"/>
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="AG4">
-        <f t="shared" si="0"/>
-        <v>6.18</v>
-      </c>
-      <c r="AH4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AI4">
-        <f t="shared" si="0"/>
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="AJ4">
-        <f t="shared" si="0"/>
-        <v>6.18</v>
       </c>
       <c r="AK4">
         <f t="shared" si="0"/>
@@ -4638,8 +4789,68 @@
         <f t="shared" si="0"/>
         <v>6.18</v>
       </c>
-    </row>
-    <row r="5" spans="2:50" x14ac:dyDescent="0.45">
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>6.18</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>6.18</v>
+      </c>
+      <c r="AZ4" s="20">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="BA4" s="20">
+        <f t="shared" si="2"/>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="BB4" s="20">
+        <f t="shared" si="3"/>
+        <v>6.18</v>
+      </c>
+      <c r="BC4" s="20">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="BD4" s="20">
+        <f t="shared" si="5"/>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="BE4" s="20">
+        <f t="shared" si="5"/>
+        <v>6.18</v>
+      </c>
+      <c r="BF4" s="20">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="BG4" s="20">
+        <f t="shared" si="7"/>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="BH4" s="20">
+        <f t="shared" si="8"/>
+        <v>6.18</v>
+      </c>
+    </row>
+    <row r="5" spans="2:60" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>217</v>
       </c>
@@ -4712,77 +4923,149 @@
       <c r="Y5">
         <v>10</v>
       </c>
-      <c r="AD5">
+      <c r="Z5" s="20">
+        <f>W5</f>
+        <v>1</v>
+      </c>
+      <c r="AA5" s="20">
+        <f t="shared" si="9"/>
+        <v>1.48</v>
+      </c>
+      <c r="AB5" s="20">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+      <c r="AC5" s="20">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AD5" s="20">
+        <f t="shared" si="9"/>
+        <v>1.48</v>
+      </c>
+      <c r="AE5" s="20">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+      <c r="AF5" s="20">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AG5" s="20">
+        <f t="shared" si="11"/>
+        <v>1.48</v>
+      </c>
+      <c r="AH5" s="20">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="13"/>
+        <v>82</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="13"/>
+        <v>1.48</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="13"/>
+        <v>1.48</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="13"/>
+        <v>1.48</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="13"/>
+        <v>1.48</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="13"/>
+        <v>1.48</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="AZ5" s="20">
         <f t="shared" si="1"/>
-        <v>82</v>
-      </c>
-      <c r="AE5">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AF5">
-        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="BA5" s="20">
+        <f t="shared" si="2"/>
         <v>1.48</v>
       </c>
-      <c r="AG5">
-        <f t="shared" si="1"/>
+      <c r="BB5" s="20">
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="AH5">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AI5">
-        <f t="shared" si="1"/>
+      <c r="BC5" s="20">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="BD5" s="20">
+        <f t="shared" si="5"/>
         <v>1.48</v>
       </c>
-      <c r="AJ5">
-        <f t="shared" si="1"/>
+      <c r="BE5" s="20">
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="AK5">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AL5">
-        <f t="shared" si="1"/>
+      <c r="BF5" s="20">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="BG5" s="20">
+        <f t="shared" si="7"/>
         <v>1.48</v>
       </c>
-      <c r="AM5">
-        <f t="shared" si="1"/>
+      <c r="BH5" s="20">
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="AN5">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AO5">
-        <f t="shared" si="1"/>
-        <v>1.48</v>
-      </c>
-      <c r="AP5">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="AQ5">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AR5">
-        <f t="shared" si="1"/>
-        <v>1.48</v>
-      </c>
-      <c r="AS5">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="2:50" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="AD7" s="2" t="s">
+    </row>
+    <row r="7" spans="2:60" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="AJ7" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="8" spans="2:50" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:60" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B8" t="s">
         <v>202</v>
       </c>
@@ -4864,91 +5147,91 @@
       <c r="AB8">
         <v>200</v>
       </c>
-      <c r="AD8" s="3" t="s">
+      <c r="AJ8" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="AE8" s="3">
-        <f t="shared" ref="AE8:AT10" si="2">I8</f>
-        <v>1</v>
-      </c>
-      <c r="AF8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AK8" s="3">
+        <f t="shared" ref="AK8:AZ10" si="14">I8</f>
+        <v>1</v>
+      </c>
+      <c r="AL8" s="3">
+        <f t="shared" si="14"/>
         <v>29</v>
       </c>
-      <c r="AG8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AM8" s="3">
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
-      <c r="AH8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AN8" s="3">
+        <f t="shared" si="14"/>
         <v>31</v>
       </c>
-      <c r="AI8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AO8" s="3">
+        <f t="shared" si="14"/>
         <v>59</v>
       </c>
-      <c r="AJ8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AP8" s="3">
+        <f t="shared" si="14"/>
         <v>60</v>
       </c>
-      <c r="AK8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AQ8" s="3">
+        <f t="shared" si="14"/>
         <v>61</v>
       </c>
-      <c r="AL8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AR8" s="3">
+        <f t="shared" si="14"/>
         <v>89</v>
       </c>
-      <c r="AM8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AS8" s="3">
+        <f t="shared" si="14"/>
         <v>90</v>
       </c>
-      <c r="AN8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AT8" s="3">
+        <f t="shared" si="14"/>
         <v>91</v>
       </c>
-      <c r="AO8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AU8" s="3">
+        <f t="shared" si="14"/>
         <v>119</v>
       </c>
-      <c r="AP8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AV8" s="3">
+        <f t="shared" si="14"/>
         <v>120</v>
       </c>
-      <c r="AQ8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AW8" s="3">
+        <f t="shared" si="14"/>
         <v>121</v>
       </c>
-      <c r="AR8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AX8" s="3">
+        <f t="shared" si="14"/>
         <v>149</v>
       </c>
-      <c r="AS8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AY8" s="3">
+        <f t="shared" si="14"/>
         <v>150</v>
       </c>
-      <c r="AT8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AZ8" s="3">
+        <f t="shared" si="14"/>
         <v>151</v>
       </c>
-      <c r="AU8" s="3">
-        <f t="shared" ref="AO8:AX10" si="3">Y8</f>
+      <c r="BA8" s="3">
+        <f t="shared" ref="AU8:BD10" si="15">Y8</f>
         <v>179</v>
       </c>
-      <c r="AV8" s="3">
-        <f t="shared" si="3"/>
+      <c r="BB8" s="3">
+        <f t="shared" si="15"/>
         <v>180</v>
       </c>
-      <c r="AW8" s="3">
-        <f t="shared" si="3"/>
+      <c r="BC8" s="3">
+        <f t="shared" si="15"/>
         <v>181</v>
       </c>
-      <c r="AX8" s="3">
-        <f t="shared" si="3"/>
+      <c r="BD8" s="3">
+        <f t="shared" si="15"/>
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="2:50" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:60" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>219</v>
       </c>
@@ -5030,92 +5313,92 @@
       <c r="AB9">
         <v>3.72</v>
       </c>
-      <c r="AD9">
-        <f t="shared" ref="AD9:AD10" si="4">H9</f>
+      <c r="AJ9">
+        <f t="shared" ref="AJ9:AJ10" si="16">H9</f>
         <v>83</v>
       </c>
-      <c r="AE9">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AF9">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AG9">
-        <f t="shared" si="2"/>
+      <c r="AK9">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AL9">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AM9">
+        <f t="shared" si="14"/>
         <v>3.72</v>
       </c>
-      <c r="AH9">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AI9">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AJ9">
-        <f t="shared" si="2"/>
+      <c r="AN9">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AO9">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AP9">
+        <f t="shared" si="14"/>
         <v>3.72</v>
       </c>
-      <c r="AK9">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AL9">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AM9">
-        <f t="shared" si="2"/>
+      <c r="AQ9">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AR9">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AS9">
+        <f t="shared" si="14"/>
         <v>3.72</v>
       </c>
-      <c r="AN9">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AO9">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AP9">
-        <f t="shared" si="3"/>
+      <c r="AT9">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AU9">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="AV9">
+        <f t="shared" si="15"/>
         <v>3.72</v>
       </c>
-      <c r="AQ9">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AR9">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AS9">
-        <f t="shared" si="3"/>
+      <c r="AW9">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="AX9">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="AY9">
+        <f t="shared" si="15"/>
         <v>3.72</v>
       </c>
-      <c r="AT9">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AU9">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AV9">
-        <f t="shared" si="3"/>
+      <c r="AZ9">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="BA9">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="BB9">
+        <f t="shared" si="15"/>
         <v>3.72</v>
       </c>
-      <c r="AW9">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AX9">
-        <f t="shared" si="3"/>
+      <c r="BC9">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="BD9">
+        <f t="shared" si="15"/>
         <v>3.72</v>
       </c>
     </row>
-    <row r="10" spans="2:50" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:60" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>221</v>
       </c>
@@ -5197,111 +5480,111 @@
       <c r="AB10">
         <v>13.27</v>
       </c>
-      <c r="AD10">
-        <f t="shared" si="4"/>
+      <c r="AJ10">
+        <f t="shared" si="16"/>
         <v>84</v>
       </c>
-      <c r="AE10">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AF10">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AG10">
-        <f t="shared" si="2"/>
+      <c r="AK10">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AL10">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AM10">
+        <f t="shared" si="14"/>
         <v>13.27</v>
       </c>
-      <c r="AH10">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AI10">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AJ10">
-        <f t="shared" si="2"/>
+      <c r="AN10">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AO10">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AP10">
+        <f t="shared" si="14"/>
         <v>13.27</v>
       </c>
-      <c r="AK10">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AL10">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AM10">
-        <f t="shared" si="2"/>
+      <c r="AQ10">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AR10">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AS10">
+        <f t="shared" si="14"/>
         <v>13.27</v>
       </c>
-      <c r="AN10">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AO10">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AP10">
-        <f t="shared" si="3"/>
+      <c r="AT10">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AU10">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="AV10">
+        <f t="shared" si="15"/>
         <v>13.27</v>
       </c>
-      <c r="AQ10">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AR10">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AS10">
-        <f t="shared" si="3"/>
+      <c r="AW10">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="AX10">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="AY10">
+        <f t="shared" si="15"/>
         <v>13.27</v>
       </c>
-      <c r="AT10">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AU10">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AV10">
-        <f t="shared" si="3"/>
+      <c r="AZ10">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="BA10">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="BB10">
+        <f t="shared" si="15"/>
         <v>13.27</v>
       </c>
-      <c r="AW10">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AX10">
-        <f t="shared" si="3"/>
+      <c r="BC10">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="BD10">
+        <f t="shared" si="15"/>
         <v>13.27</v>
       </c>
     </row>
-    <row r="13" spans="2:50" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:60" x14ac:dyDescent="0.45">
       <c r="B13" s="16" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="2:50" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:60" x14ac:dyDescent="0.45">
       <c r="B14" s="18" t="s">
         <v>223</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
     </row>
-    <row r="15" spans="2:50" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:60" x14ac:dyDescent="0.45">
       <c r="B15" s="18" t="s">
         <v>224</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
     </row>
-    <row r="16" spans="2:50" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:60" x14ac:dyDescent="0.45">
       <c r="B16" s="18" t="s">
         <v>225</v>
       </c>
@@ -5390,7 +5673,7 @@
         <v>246</v>
       </c>
       <c r="K22">
-        <f>AD4</f>
+        <f>AJ4</f>
         <v>81</v>
       </c>
       <c r="L22">
@@ -5414,7 +5697,7 @@
         <v>80</v>
       </c>
       <c r="K23">
-        <f>AD5</f>
+        <f>AJ5</f>
         <v>82</v>
       </c>
       <c r="L23">
@@ -5438,7 +5721,7 @@
         <v>22</v>
       </c>
       <c r="K24">
-        <f>AD9</f>
+        <f>AJ9</f>
         <v>83</v>
       </c>
       <c r="L24">
@@ -5462,7 +5745,7 @@
         <v>15</v>
       </c>
       <c r="K25">
-        <f>AD10</f>
+        <f>AJ10</f>
         <v>84</v>
       </c>
       <c r="L25">
